--- a/models/mast3r/mast3r_results.xlsx
+++ b/models/mast3r/mast3r_results.xlsx
@@ -4842,76 +4842,76 @@
         <v>3</v>
       </c>
       <c r="M30">
-        <v>2.943112581000605</v>
+        <v>2.7841347489998043</v>
       </c>
       <c r="N30">
-        <v>10.411801727999773</v>
+        <v>8.871440200000052</v>
       </c>
       <c r="O30">
-        <v>20.905738577001102</v>
+        <v>20.234605023999848</v>
       </c>
       <c r="P30">
-        <v>63.640602522000336</v>
+        <v>60.36602120999987</v>
       </c>
       <c r="Q30">
-        <v>77.18972274599946</v>
+        <v>72.22459373399988</v>
       </c>
       <c r="R30">
-        <v>3.927548588000718</v>
+        <v>3.498470808000093</v>
       </c>
       <c r="S30">
-        <v>3.8676337160013645</v>
+        <v>3.4062608250001176</v>
       </c>
       <c r="T30">
-        <v>3.9627267610012495</v>
+        <v>3.659247343000061</v>
       </c>
       <c r="U30">
-        <v>16.50177022400021</v>
+        <v>16.09504743999969</v>
       </c>
       <c r="V30">
-        <v>16.382930805999422</v>
+        <v>15.476479203000054</v>
       </c>
       <c r="W30">
-        <v>17.33020504399974</v>
+        <v>16.7090917620003</v>
       </c>
       <c r="X30">
-        <v>0.047583587000190164</v>
+        <v>0.04855428099972414</v>
       </c>
       <c r="Y30">
-        <v>0.04740797099839256</v>
+        <v>0.04813538999997036</v>
       </c>
       <c r="Z30">
-        <v>0.06930666500011284</v>
+        <v>0.05792313499978263</v>
       </c>
       <c r="AA30">
-        <v>0.45602872199924605</v>
+        <v>0.43175368600032016</v>
       </c>
       <c r="AB30">
-        <v>0.4285701299995708</v>
+        <v>0.4117616739999903</v>
       </c>
       <c r="AC30">
-        <v>0.5137250739990122</v>
+        <v>0.4950868209998589</v>
       </c>
       <c r="AD30">
-        <v>20.84968635900077</v>
+        <v>19.435700302999976</v>
       </c>
       <c r="AE30">
-        <v>21.781307364000895</v>
+        <v>20.6687551910004</v>
       </c>
       <c r="AF30">
-        <v>5977.38671875</v>
+        <v>5965.8125</v>
       </c>
       <c r="AG30">
-        <v>1954.359375</v>
+        <v>1960.78515625</v>
       </c>
       <c r="AH30">
-        <v>1676.44921875</v>
+        <v>1681.1640625</v>
       </c>
       <c r="AI30">
-        <v>1999.88671875</v>
+        <v>2004.09765625</v>
       </c>
       <c r="AJ30">
-        <v>5977.76171875</v>
+        <v>5965.3203125</v>
       </c>
       <c r="AK30">
         <v>2636.826171875</v>
@@ -8976,76 +8976,76 @@
         <v>3</v>
       </c>
       <c r="M56">
-        <v>2.920043861999602</v>
+        <v>2.8555368249999447</v>
       </c>
       <c r="N56">
-        <v>10.289346491000288</v>
+        <v>10.18591980500014</v>
       </c>
       <c r="O56">
-        <v>10.500424769999881</v>
+        <v>9.734811131000242</v>
       </c>
       <c r="P56">
-        <v>31.741927388000022</v>
+        <v>29.736050877000253</v>
       </c>
       <c r="Q56">
-        <v>45.132979245000115</v>
+        <v>42.97492976800004</v>
       </c>
       <c r="R56">
-        <v>1.9786930630002644</v>
+        <v>1.861260793999918</v>
       </c>
       <c r="S56">
-        <v>1.885584869000013</v>
+        <v>1.7083769360001497</v>
       </c>
       <c r="T56">
-        <v>2.0748243139996703</v>
+        <v>1.867692328999965</v>
       </c>
       <c r="U56">
-        <v>8.311724782000056</v>
+        <v>7.675539765999929</v>
       </c>
       <c r="V56">
-        <v>7.927611273999901</v>
+        <v>7.624450409000019</v>
       </c>
       <c r="W56">
-        <v>8.878946895999889</v>
+        <v>8.35066889699965</v>
       </c>
       <c r="X56">
-        <v>0.019322709000334726</v>
+        <v>0.018128994000107923</v>
       </c>
       <c r="Y56">
-        <v>0.01902970400033155</v>
+        <v>0.016503424999882554</v>
       </c>
       <c r="Z56">
-        <v>0.024818192000111594</v>
+        <v>0.02230210400011856</v>
       </c>
       <c r="AA56">
-        <v>0.19057771500001763</v>
+        <v>0.19404354099970078</v>
       </c>
       <c r="AB56">
-        <v>0.1871326229997976</v>
+        <v>0.17310001799978636</v>
       </c>
       <c r="AC56">
-        <v>0.21473762100004024</v>
+        <v>0.21034746600025755</v>
       </c>
       <c r="AD56">
-        <v>10.209239165999861</v>
+        <v>9.69661063500007</v>
       </c>
       <c r="AE56">
-        <v>11.004511044000083</v>
+        <v>10.292169529000148</v>
       </c>
       <c r="AF56">
-        <v>5977.1015625</v>
+        <v>5965.83984375</v>
       </c>
       <c r="AG56">
-        <v>1925.23046875</v>
+        <v>1918.1328125</v>
       </c>
       <c r="AH56">
-        <v>1591.484375</v>
+        <v>1586.7109375</v>
       </c>
       <c r="AI56">
-        <v>1933.1875</v>
+        <v>1919.87890625</v>
       </c>
       <c r="AJ56">
-        <v>5977.6015625</v>
+        <v>5965.32421875</v>
       </c>
       <c r="AK56">
         <v>2636.826171875</v>
@@ -9063,13 +9063,13 @@
         <v>3156.44140625</v>
       </c>
       <c r="AP56">
-        <v>4074.0</v>
+        <v>3802.0</v>
       </c>
       <c r="AQ56">
-        <v>4024.0</v>
+        <v>3752.0</v>
       </c>
       <c r="AR56">
-        <v>4074.0</v>
+        <v>3802.0</v>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
@@ -9612,76 +9612,76 @@
         <v>3</v>
       </c>
       <c r="M60">
-        <v>2.941438435999771</v>
+        <v>3.1848892930001966</v>
       </c>
       <c r="N60">
-        <v>10.447108911999749</v>
+        <v>9.30141459000015</v>
       </c>
       <c r="O60">
-        <v>22.099702094999884</v>
+        <v>21.41903684800036</v>
       </c>
       <c r="P60">
-        <v>67.38911411199933</v>
+        <v>64.47596836999992</v>
       </c>
       <c r="Q60">
-        <v>80.96983109700068</v>
+        <v>77.14022123800032</v>
       </c>
       <c r="R60">
-        <v>3.9620475689998784</v>
+        <v>3.4975107179998304</v>
       </c>
       <c r="S60">
-        <v>3.9521554769999057</v>
+        <v>3.477004074999968</v>
       </c>
       <c r="T60">
-        <v>4.164520769999399</v>
+        <v>3.542695786999957</v>
       </c>
       <c r="U60">
-        <v>17.572775489000378</v>
+        <v>17.501153875</v>
       </c>
       <c r="V60">
-        <v>17.532014401000197</v>
+        <v>17.20762151200006</v>
       </c>
       <c r="W60">
-        <v>18.843055701000594</v>
+        <v>18.07114566400014</v>
       </c>
       <c r="X60">
-        <v>0.04969440199965902</v>
+        <v>0.04872126500004015</v>
       </c>
       <c r="Y60">
-        <v>0.04850991800049087</v>
+        <v>0.04067526300013924</v>
       </c>
       <c r="Z60">
-        <v>0.07183238099969458</v>
+        <v>0.05689982800004145</v>
       </c>
       <c r="AA60">
-        <v>0.35423399600040284</v>
+        <v>0.3340955680000661</v>
       </c>
       <c r="AB60">
-        <v>0.3394549160002498</v>
+        <v>0.31648983800005226</v>
       </c>
       <c r="AC60">
-        <v>0.4011394039998777</v>
+        <v>0.35416211299980205</v>
       </c>
       <c r="AD60">
-        <v>21.91445265600032</v>
+        <v>21.07072880199985</v>
       </c>
       <c r="AE60">
-        <v>23.278505676999885</v>
+        <v>21.959648455000206</v>
       </c>
       <c r="AF60">
-        <v>5976.7265625</v>
+        <v>5965.76953125</v>
       </c>
       <c r="AG60">
-        <v>1945.07421875</v>
+        <v>1936.00390625</v>
       </c>
       <c r="AH60">
-        <v>1655.05859375</v>
+        <v>1647.94921875</v>
       </c>
       <c r="AI60">
-        <v>1988.03515625</v>
+        <v>1964.5546875</v>
       </c>
       <c r="AJ60">
-        <v>5977.1015625</v>
+        <v>5965.578125</v>
       </c>
       <c r="AK60">
         <v>2636.826171875</v>
@@ -9699,13 +9699,13 @@
         <v>3246.98388671875</v>
       </c>
       <c r="AP60">
-        <v>4204.0</v>
+        <v>3948.0</v>
       </c>
       <c r="AQ60">
-        <v>4204.0</v>
+        <v>3948.0</v>
       </c>
       <c r="AR60">
-        <v>4252.0</v>
+        <v>3996.0</v>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
@@ -11361,76 +11361,76 @@
         <v>3</v>
       </c>
       <c r="M71">
-        <v>3.0988415580000037</v>
+        <v>5.296692034999978</v>
       </c>
       <c r="N71">
-        <v>10.679393852999965</v>
+        <v>10.900818075999723</v>
       </c>
       <c r="O71">
-        <v>9.603791856000043</v>
+        <v>8.500333046999913</v>
       </c>
       <c r="P71">
-        <v>29.83914722199961</v>
+        <v>27.046133827000176</v>
       </c>
       <c r="Q71">
-        <v>43.80151377000038</v>
+        <v>43.45614949999981</v>
       </c>
       <c r="R71">
-        <v>1.1236485960002938</v>
+        <v>0.9774719870001718</v>
       </c>
       <c r="S71">
-        <v>1.1220896750000975</v>
+        <v>0.9715561920002074</v>
       </c>
       <c r="T71">
-        <v>1.1508238060000622</v>
+        <v>1.0333669579999878</v>
       </c>
       <c r="U71">
-        <v>8.279828586999884</v>
+        <v>7.323776796999937</v>
       </c>
       <c r="V71">
-        <v>8.214029729999766</v>
+        <v>7.225158592000298</v>
       </c>
       <c r="W71">
-        <v>9.308630717000142</v>
+        <v>8.783771259999867</v>
       </c>
       <c r="X71">
-        <v>0.019188774999747693</v>
+        <v>0.01713041599987264</v>
       </c>
       <c r="Y71">
-        <v>0.01902949700024692</v>
+        <v>0.015616743000009592</v>
       </c>
       <c r="Z71">
-        <v>0.025243373999728647</v>
+        <v>0.022517621999668336</v>
       </c>
       <c r="AA71">
-        <v>0.18094180800017057</v>
+        <v>0.2211561310000434</v>
       </c>
       <c r="AB71">
-        <v>0.17995708399985233</v>
+        <v>0.18903571999999258</v>
       </c>
       <c r="AC71">
-        <v>0.1887171280000075</v>
+        <v>0.2541241090002586</v>
       </c>
       <c r="AD71">
-        <v>9.564404023999941</v>
+        <v>8.441266227000142</v>
       </c>
       <c r="AE71">
-        <v>10.645059962999767</v>
+        <v>10.09424468599991</v>
       </c>
       <c r="AF71">
-        <v>5976.53515625</v>
+        <v>5964.32421875</v>
       </c>
       <c r="AG71">
-        <v>1757.9296875</v>
+        <v>1766.15234375</v>
       </c>
       <c r="AH71">
-        <v>1601.93359375</v>
+        <v>1626.37890625</v>
       </c>
       <c r="AI71">
-        <v>1776.30859375</v>
+        <v>1780.10546875</v>
       </c>
       <c r="AJ71">
-        <v>5976.91015625</v>
+        <v>5964.046875</v>
       </c>
       <c r="AK71">
         <v>2636.826171875</v>
@@ -11448,13 +11448,13 @@
         <v>3090.45263671875</v>
       </c>
       <c r="AP71">
-        <v>3882.0</v>
+        <v>3904.0</v>
       </c>
       <c r="AQ71">
-        <v>3776.0</v>
+        <v>3798.0</v>
       </c>
       <c r="AR71">
-        <v>3882.0</v>
+        <v>3904.0</v>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
@@ -23638,28 +23638,28 @@
         <v>1</v>
       </c>
       <c r="G86">
-        <v>3.8676337160013645</v>
+        <v>3.4062608250001176</v>
       </c>
       <c r="H86">
-        <v>17.33020504399974</v>
+        <v>16.7090917620003</v>
       </c>
       <c r="I86">
-        <v>0.06930666500011284</v>
+        <v>0.05792313499978263</v>
       </c>
       <c r="J86">
-        <v>0.5137250739990122</v>
+        <v>0.4950868209998589</v>
       </c>
       <c r="K86">
-        <v>21.781307364000895</v>
+        <v>20.6687551910004</v>
       </c>
       <c r="L86">
-        <v>761.71484375</v>
+        <v>750.0859375</v>
       </c>
       <c r="M86">
-        <v>1609.1953125</v>
+        <v>1615.40625</v>
       </c>
       <c r="N86">
-        <v>1676.44921875</v>
+        <v>1681.1640625</v>
       </c>
       <c r="O86">
         <v>3237.205078125</v>
@@ -23698,28 +23698,28 @@
         <v>2</v>
       </c>
       <c r="G87">
-        <v>3.9627267610012495</v>
+        <v>3.659247343000061</v>
       </c>
       <c r="H87">
-        <v>16.382930805999422</v>
+        <v>16.09504743999969</v>
       </c>
       <c r="I87">
-        <v>0.047583587000190164</v>
+        <v>0.04813538999997036</v>
       </c>
       <c r="J87">
-        <v>0.45602872199924605</v>
+        <v>0.43175368600032016</v>
       </c>
       <c r="K87">
-        <v>20.84968635900077</v>
+        <v>20.234605023999848</v>
       </c>
       <c r="L87">
-        <v>1608.609375</v>
+        <v>1614.8984375</v>
       </c>
       <c r="M87">
-        <v>1637.92578125</v>
+        <v>1642.21484375</v>
       </c>
       <c r="N87">
-        <v>1954.359375</v>
+        <v>1960.78515625</v>
       </c>
       <c r="O87">
         <v>3247.0498046875</v>
@@ -23758,28 +23758,28 @@
         <v>3</v>
       </c>
       <c r="G88">
-        <v>3.927548588000718</v>
+        <v>3.498470808000093</v>
       </c>
       <c r="H88">
-        <v>16.50177022400021</v>
+        <v>15.476479203000054</v>
       </c>
       <c r="I88">
-        <v>0.04740797099839256</v>
+        <v>0.04855428099972414</v>
       </c>
       <c r="J88">
-        <v>0.4285701299995708</v>
+        <v>0.4117616739999903</v>
       </c>
       <c r="K88">
-        <v>20.905738577001102</v>
+        <v>19.435700302999976</v>
       </c>
       <c r="L88">
-        <v>1637.92578125</v>
+        <v>1642.21484375</v>
       </c>
       <c r="M88">
-        <v>1638.30859375</v>
+        <v>1646.765625</v>
       </c>
       <c r="N88">
-        <v>1999.88671875</v>
+        <v>2004.09765625</v>
       </c>
       <c r="O88">
         <v>3247.0498046875</v>
@@ -28318,34 +28318,34 @@
         <v>1</v>
       </c>
       <c r="G164">
-        <v>1.885584869000013</v>
+        <v>1.7083769360001497</v>
       </c>
       <c r="H164">
-        <v>8.878946895999889</v>
+        <v>8.35066889699965</v>
       </c>
       <c r="I164">
-        <v>0.024818192000111594</v>
+        <v>0.02230210400011856</v>
       </c>
       <c r="J164">
-        <v>0.21473762100004024</v>
+        <v>0.21034746600025755</v>
       </c>
       <c r="K164">
-        <v>11.004511044000083</v>
+        <v>10.292169529000148</v>
       </c>
       <c r="L164">
-        <v>761.58203125</v>
+        <v>750.171875</v>
       </c>
       <c r="M164">
-        <v>1583.6796875</v>
+        <v>1578.82421875</v>
       </c>
       <c r="N164">
-        <v>1591.484375</v>
+        <v>1586.7109375</v>
       </c>
       <c r="O164">
         <v>3145.69091796875</v>
       </c>
       <c r="P164">
-        <v>4024.0</v>
+        <v>3752.0</v>
       </c>
     </row>
     <row r="165">
@@ -28378,34 +28378,34 @@
         <v>2</v>
       </c>
       <c r="G165">
-        <v>2.0748243139996703</v>
+        <v>1.861260793999918</v>
       </c>
       <c r="H165">
-        <v>7.927611273999901</v>
+        <v>7.624450409000019</v>
       </c>
       <c r="I165">
-        <v>0.019322709000334726</v>
+        <v>0.016503424999882554</v>
       </c>
       <c r="J165">
-        <v>0.1871326229997976</v>
+        <v>0.19404354099970078</v>
       </c>
       <c r="K165">
-        <v>10.209239165999861</v>
+        <v>9.69661063500007</v>
       </c>
       <c r="L165">
-        <v>1583.6796875</v>
+        <v>1578.82421875</v>
       </c>
       <c r="M165">
-        <v>1581.640625</v>
+        <v>1577.47265625</v>
       </c>
       <c r="N165">
-        <v>1925.23046875</v>
+        <v>1918.1328125</v>
       </c>
       <c r="O165">
         <v>3156.44140625</v>
       </c>
       <c r="P165">
-        <v>4074.0</v>
+        <v>3802.0</v>
       </c>
     </row>
     <row r="166">
@@ -28438,34 +28438,34 @@
         <v>3</v>
       </c>
       <c r="G166">
-        <v>1.9786930630002644</v>
+        <v>1.867692328999965</v>
       </c>
       <c r="H166">
-        <v>8.311724782000056</v>
+        <v>7.675539765999929</v>
       </c>
       <c r="I166">
-        <v>0.01902970400033155</v>
+        <v>0.018128994000107923</v>
       </c>
       <c r="J166">
-        <v>0.19057771500001763</v>
+        <v>0.17310001799978636</v>
       </c>
       <c r="K166">
-        <v>10.500424769999881</v>
+        <v>9.734811131000242</v>
       </c>
       <c r="L166">
-        <v>1581.640625</v>
+        <v>1577.47265625</v>
       </c>
       <c r="M166">
-        <v>1581.7265625</v>
+        <v>1579.76953125</v>
       </c>
       <c r="N166">
-        <v>1933.1875</v>
+        <v>1919.87890625</v>
       </c>
       <c r="O166">
         <v>3156.44140625</v>
       </c>
       <c r="P166">
-        <v>4074.0</v>
+        <v>3802.0</v>
       </c>
     </row>
     <row r="167">
@@ -29038,34 +29038,34 @@
         <v>1</v>
       </c>
       <c r="G176">
-        <v>3.9620475689998784</v>
+        <v>3.477004074999968</v>
       </c>
       <c r="H176">
-        <v>18.843055701000594</v>
+        <v>18.07114566400014</v>
       </c>
       <c r="I176">
-        <v>0.07183238099969458</v>
+        <v>0.05689982800004145</v>
       </c>
       <c r="J176">
-        <v>0.4011394039998777</v>
+        <v>0.35416211299980205</v>
       </c>
       <c r="K176">
-        <v>23.278505676999885</v>
+        <v>21.959648455000206</v>
       </c>
       <c r="L176">
-        <v>761.05078125</v>
+        <v>750.04296875</v>
       </c>
       <c r="M176">
-        <v>1599.26171875</v>
+        <v>1590.1171875</v>
       </c>
       <c r="N176">
-        <v>1655.05859375</v>
+        <v>1647.94921875</v>
       </c>
       <c r="O176">
         <v>3237.1494140625</v>
       </c>
       <c r="P176">
-        <v>4252.0</v>
+        <v>3996.0</v>
       </c>
     </row>
     <row r="177">
@@ -29098,34 +29098,34 @@
         <v>2</v>
       </c>
       <c r="G177">
-        <v>4.164520769999399</v>
+        <v>3.542695786999957</v>
       </c>
       <c r="H177">
-        <v>17.532014401000197</v>
+        <v>17.501153875</v>
       </c>
       <c r="I177">
-        <v>0.04850991800049087</v>
+        <v>0.04067526300013924</v>
       </c>
       <c r="J177">
-        <v>0.35423399600040284</v>
+        <v>0.3340955680000661</v>
       </c>
       <c r="K177">
-        <v>22.099702094999884</v>
+        <v>21.41903684800036</v>
       </c>
       <c r="L177">
-        <v>1599.26171875</v>
+        <v>1590.1171875</v>
       </c>
       <c r="M177">
-        <v>1662.484375</v>
+        <v>1655.6796875</v>
       </c>
       <c r="N177">
-        <v>1945.07421875</v>
+        <v>1936.00390625</v>
       </c>
       <c r="O177">
         <v>3246.98388671875</v>
       </c>
       <c r="P177">
-        <v>4204.0</v>
+        <v>3948.0</v>
       </c>
     </row>
     <row r="178">
@@ -29158,34 +29158,34 @@
         <v>3</v>
       </c>
       <c r="G178">
-        <v>3.9521554769999057</v>
+        <v>3.4975107179998304</v>
       </c>
       <c r="H178">
-        <v>17.572775489000378</v>
+        <v>17.20762151200006</v>
       </c>
       <c r="I178">
-        <v>0.04969440199965902</v>
+        <v>0.04872126500004015</v>
       </c>
       <c r="J178">
-        <v>0.3394549160002498</v>
+        <v>0.31648983800005226</v>
       </c>
       <c r="K178">
-        <v>21.91445265600032</v>
+        <v>21.07072880199985</v>
       </c>
       <c r="L178">
-        <v>1662.484375</v>
+        <v>1655.6796875</v>
       </c>
       <c r="M178">
-        <v>1623.36328125</v>
+        <v>1651.453125</v>
       </c>
       <c r="N178">
-        <v>1988.03515625</v>
+        <v>1964.5546875</v>
       </c>
       <c r="O178">
         <v>3246.98388671875</v>
       </c>
       <c r="P178">
-        <v>4204.0</v>
+        <v>3948.0</v>
       </c>
     </row>
     <row r="179">
@@ -31018,34 +31018,34 @@
         <v>1</v>
       </c>
       <c r="G209">
-        <v>1.1220896750000975</v>
+        <v>1.0333669579999878</v>
       </c>
       <c r="H209">
-        <v>9.308630717000142</v>
+        <v>8.783771259999867</v>
       </c>
       <c r="I209">
-        <v>0.025243373999728647</v>
+        <v>0.022517621999668336</v>
       </c>
       <c r="J209">
-        <v>0.1887171280000075</v>
+        <v>0.2541241090002586</v>
       </c>
       <c r="K209">
-        <v>10.645059962999767</v>
+        <v>10.09424468599991</v>
       </c>
       <c r="L209">
-        <v>760.703125</v>
+        <v>748.60546875</v>
       </c>
       <c r="M209">
-        <v>1601.93359375</v>
+        <v>1620.4765625</v>
       </c>
       <c r="N209">
-        <v>1601.93359375</v>
+        <v>1626.37890625</v>
       </c>
       <c r="O209">
         <v>3083.3583984375</v>
       </c>
       <c r="P209">
-        <v>3776.0</v>
+        <v>3798.0</v>
       </c>
     </row>
     <row r="210">
@@ -31078,34 +31078,34 @@
         <v>2</v>
       </c>
       <c r="G210">
-        <v>1.1508238060000622</v>
+        <v>0.9774719870001718</v>
       </c>
       <c r="H210">
-        <v>8.214029729999766</v>
+        <v>7.225158592000298</v>
       </c>
       <c r="I210">
-        <v>0.019188774999747693</v>
+        <v>0.01713041599987264</v>
       </c>
       <c r="J210">
-        <v>0.17995708399985233</v>
+        <v>0.2211561310000434</v>
       </c>
       <c r="K210">
-        <v>9.564404023999941</v>
+        <v>8.441266227000142</v>
       </c>
       <c r="L210">
-        <v>1601.93359375</v>
+        <v>1620.4765625</v>
       </c>
       <c r="M210">
-        <v>1602.4296875</v>
+        <v>1631.640625</v>
       </c>
       <c r="N210">
-        <v>1776.30859375</v>
+        <v>1766.15234375</v>
       </c>
       <c r="O210">
         <v>3090.45263671875</v>
       </c>
       <c r="P210">
-        <v>3882.0</v>
+        <v>3904.0</v>
       </c>
     </row>
     <row r="211">
@@ -31138,34 +31138,34 @@
         <v>3</v>
       </c>
       <c r="G211">
-        <v>1.1236485960002938</v>
+        <v>0.9715561920002074</v>
       </c>
       <c r="H211">
-        <v>8.279828586999884</v>
+        <v>7.323776796999937</v>
       </c>
       <c r="I211">
-        <v>0.01902949700024692</v>
+        <v>0.015616743000009592</v>
       </c>
       <c r="J211">
-        <v>0.18094180800017057</v>
+        <v>0.18903571999999258</v>
       </c>
       <c r="K211">
-        <v>9.603791856000043</v>
+        <v>8.500333046999913</v>
       </c>
       <c r="L211">
-        <v>1602.4296875</v>
+        <v>1631.640625</v>
       </c>
       <c r="M211">
-        <v>1604.62109375</v>
+        <v>1620.71875</v>
       </c>
       <c r="N211">
-        <v>1757.9296875</v>
+        <v>1780.10546875</v>
       </c>
       <c r="O211">
         <v>3090.45263671875</v>
       </c>
       <c r="P211">
-        <v>3882.0</v>
+        <v>3904.0</v>
       </c>
     </row>
     <row r="212">
@@ -44381,12 +44381,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8737.jpg</t>
+          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8740.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>IMG_8737.jpg</t>
+          <t>IMG_8740.jpg</t>
         </is>
       </c>
     </row>
@@ -49301,12 +49301,12 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8785.jpg</t>
+          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8787.jpg</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>IMG_8785.jpg</t>
+          <t>IMG_8787.jpg</t>
         </is>
       </c>
     </row>
@@ -50021,12 +50021,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8862.jpg</t>
+          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8861.jpg</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>IMG_8862.jpg</t>
+          <t>IMG_8861.jpg</t>
         </is>
       </c>
     </row>
@@ -52101,12 +52101,12 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1782.JPG</t>
+          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1768.JPG</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>DSC_1782.JPG</t>
+          <t>DSC_1768.JPG</t>
         </is>
       </c>
     </row>
@@ -60464,7 +60464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10T17:07:57+00:00</t>
+          <t>2026-08-17T10:03:42+00:00</t>
         </is>
       </c>
     </row>
